--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 14:39</t>
+          <t>2026-05-08 16:05</t>
         </is>
       </c>
     </row>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05</t>
+          <t>2026-05-08 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -109,7 +109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:26</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:26</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NoWork_Outbound_50pct" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NoWork_Outbound_50pct" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NoWork_Outbound_50pct'!$A$4:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NoWork_Outbound_50pct'!$A$4:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-05-26 13:09</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -579,24 +579,24 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>6500</v>
+        <v>7432.03</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3250</v>
+        <v>3716</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>No-work recovery: anchor 2026-04-25 (Dest_In of chosen trip 2026-04-25)</t>
+          <t>No-work recovery: anchor 2026-05-02 (Dest_In of chosen trip 2026-05-03)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -610,28 +610,28 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>6500</v>
+        <v>7432.03</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3250</v>
+        <v>3716</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>No-work recovery: anchor 2026-04-25 (Dest_In of chosen trip 2026-04-25)</t>
+          <t>No-work recovery: anchor 2026-05-02 (Dest_In of chosen trip 2026-05-02)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -641,28 +641,28 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6500</v>
+        <v>7432.03</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3250</v>
+        <v>3716</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>No-work recovery: anchor 2026-04-25 (Dest_In of chosen trip 2026-04-26)</t>
+          <t>No-work recovery: anchor 2026-05-02 (Dest_In of chosen trip 2026-05-04)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -672,147 +672,23 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6500</v>
+        <v>7432.03</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3250</v>
+        <v>3716</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>No-work recovery: anchor 2026-04-25 (Dest_In of chosen trip 2026-04-25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>46141</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>14.8</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>3250</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>No-work recovery: anchor 2026-04-29 (Dest_In of chosen trip 2026-04-29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>46141</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>71-6802</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>10.20</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>3250</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>No-work recovery: anchor 2026-04-29 (Dest_In of chosen trip 2026-04-30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>46141</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>71-8681</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>9.13</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>3250</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>No-work recovery: anchor 2026-04-29 (Dest_In of chosen trip 2026-04-29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>46141</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>71-9629</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>8.20</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>3250</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>No-work recovery: anchor 2026-04-29 (Dest_In of chosen trip 2026-04-29)</t>
+          <t>No-work recovery: anchor 2026-05-02 (Dest_In of chosen trip 2026-05-03)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G12"/>
+  <autoFilter ref="A4:G8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:09</t>
+          <t>2026-05-26 13:16</t>
         </is>
       </c>
     </row>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:16</t>
+          <t>2026-05-26 13:20</t>
         </is>
       </c>
     </row>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NoWork_Outbound_50pct" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NoWork_Outbound_50pct'!$A$4:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NoWork_Outbound_50pct'!$A$4:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -49,7 +47,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -59,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F7FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -102,24 +95,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,16 +461,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -513,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:20</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -563,132 +538,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>46144</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>No-work recovery: anchor 2026-05-02 (Dest_In of chosen trip 2026-05-03)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>46144</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>71-6802</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>3716</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>No-work recovery: anchor 2026-05-02 (Dest_In of chosen trip 2026-05-02)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>46144</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>No-work recovery: anchor 2026-05-02 (Dest_In of chosen trip 2026-05-04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>46144</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>72-1218</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>3716</v>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>No-work recovery: anchor 2026-05-02 (Dest_In of chosen trip 2026-05-03)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G8"/>
+  <autoFilter ref="A4:G4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:49</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 18:21</t>
+          <t>2026-08-04 14:01</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:01</t>
+          <t>2026-08-04 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:33</t>
+          <t>2026-08-04 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:11</t>
+          <t>2026-08-05 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 14:34</t>
+          <t>2026-08-07 15:55</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 15:55</t>
+          <t>2026-08-09 10:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
+++ b/reports/oatside-pg-2026/exports/12_NoWork_Outbound_50pct.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:57</t>
+          <t>2026-08-09 11:52</t>
         </is>
       </c>
     </row>
